--- a/魔物娘TD_名字编号属性对照表.xlsx
+++ b/魔物娘TD_名字编号属性对照表.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="2074">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2075" uniqueCount="2075">
   <si>
     <r>
       <t>编号</t>
@@ -8202,6 +8202,9 @@
     <r>
       <t>デスワーム娘</t>
     </r>
+  </si>
+  <si>
+    <t>へディア</t>
   </si>
   <si>
     <r>
@@ -10951,7 +10954,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -10961,6 +10964,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf fontId="19" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
@@ -32856,8 +32862,8 @@
       <c r="C327" s="3" t="s">
         <v>1636</v>
       </c>
-      <c r="D327" s="3" t="s">
-        <v>909</v>
+      <c r="D327" s="6" t="s">
+        <v>1637</v>
       </c>
       <c r="E327" s="4"/>
       <c r="F327" s="3" t="s">
@@ -32918,7 +32924,7 @@
         <v>23</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="D328" s="3" t="s">
         <v>582</v>
@@ -32949,7 +32955,7 @@
         <v>50</v>
       </c>
       <c r="N328" s="3" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="O328" s="3" t="s">
         <v>1002</v>
@@ -32978,13 +32984,13 @@
     </row>
     <row r="329">
       <c r="A329" s="3" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="D329" s="3" t="s">
         <v>435</v>
@@ -33000,7 +33006,7 @@
         <v>385</v>
       </c>
       <c r="I329" s="3" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="J329" s="3" t="s">
         <v>155</v>
@@ -33015,7 +33021,7 @@
         <v>50</v>
       </c>
       <c r="N329" s="3" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="O329" s="3" t="s">
         <v>1610</v>
@@ -33044,13 +33050,13 @@
     </row>
     <row r="330">
       <c r="A330" s="3" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="D330" s="3" t="s">
         <v>330</v>
@@ -33116,14 +33122,14 @@
         <v>72</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="E331" s="4"/>
       <c r="F331" s="3" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="G331" s="3" t="s">
         <v>62</v>
@@ -33176,16 +33182,16 @@
     </row>
     <row r="332">
       <c r="A332" s="3" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="E332" s="4"/>
       <c r="F332" s="3" t="s">
@@ -33242,20 +33248,20 @@
     </row>
     <row r="333">
       <c r="A333" s="3" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="E333" s="4"/>
       <c r="F333" s="3" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="G333" s="3" t="s">
         <v>154</v>
@@ -33314,14 +33320,14 @@
         <v>23</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="E334" s="4"/>
       <c r="F334" s="3" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="G334" s="3" t="s">
         <v>146</v>
@@ -33345,7 +33351,7 @@
         <v>32</v>
       </c>
       <c r="N334" s="3" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="O334" s="3" t="s">
         <v>1509</v>
@@ -33374,20 +33380,20 @@
     </row>
     <row r="335">
       <c r="A335" s="3" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C335" s="3" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="E335" s="4"/>
       <c r="F335" s="3" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="G335" s="3" t="s">
         <v>154</v>
@@ -33411,7 +33417,7 @@
         <v>50</v>
       </c>
       <c r="N335" s="3" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="O335" s="3" t="s">
         <v>763</v>
@@ -33446,14 +33452,14 @@
         <v>23</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="E336" s="4"/>
       <c r="F336" s="3" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="G336" s="3" t="s">
         <v>87</v>
@@ -33477,7 +33483,7 @@
         <v>50</v>
       </c>
       <c r="N336" s="3" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="O336" s="3" t="s">
         <v>438</v>
@@ -33512,7 +33518,7 @@
         <v>72</v>
       </c>
       <c r="C337" s="3" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="D337" s="3" t="s">
         <v>85</v>
@@ -33540,7 +33546,7 @@
         <v>32</v>
       </c>
       <c r="N337" s="3" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="O337" s="3" t="s">
         <v>1509</v>
@@ -33569,20 +33575,20 @@
     </row>
     <row r="338">
       <c r="A338" s="3" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="E338" s="4"/>
       <c r="F338" s="3" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="G338" s="3" t="s">
         <v>154</v>
@@ -33591,7 +33597,7 @@
         <v>385</v>
       </c>
       <c r="I338" s="3" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="J338" s="3" t="s">
         <v>761</v>
@@ -33635,20 +33641,20 @@
     </row>
     <row r="339">
       <c r="A339" s="3" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="E339" s="4"/>
       <c r="F339" s="3" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="G339" s="3" t="s">
         <v>172</v>
@@ -33672,7 +33678,7 @@
         <v>50</v>
       </c>
       <c r="N339" s="3" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="O339" s="3" t="s">
         <v>944</v>
@@ -33701,20 +33707,20 @@
     </row>
     <row r="340">
       <c r="A340" s="3" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="E340" s="4"/>
       <c r="F340" s="3" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="G340" s="3" t="s">
         <v>62</v>
@@ -33738,7 +33744,7 @@
         <v>50</v>
       </c>
       <c r="N340" s="3" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="O340" s="3" t="s">
         <v>1335</v>
@@ -33773,14 +33779,14 @@
         <v>23</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="E341" s="4"/>
       <c r="F341" s="3" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="G341" s="3" t="s">
         <v>146</v>
@@ -33792,7 +33798,7 @@
         <v>63</v>
       </c>
       <c r="J341" s="3" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="K341" s="3" t="s">
         <v>48</v>
@@ -33804,7 +33810,7 @@
         <v>50</v>
       </c>
       <c r="N341" s="3" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="O341" s="3" t="s">
         <v>485</v>
@@ -33833,20 +33839,20 @@
     </row>
     <row r="342">
       <c r="A342" s="3" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>72</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="E342" s="4"/>
       <c r="F342" s="3" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="G342" s="3" t="s">
         <v>154</v>
@@ -33899,20 +33905,20 @@
     </row>
     <row r="343">
       <c r="A343" s="3" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C343" s="3" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="E343" s="4"/>
       <c r="F343" s="3" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="G343" s="3" t="s">
         <v>27</v>
@@ -33936,7 +33942,7 @@
         <v>50</v>
       </c>
       <c r="N343" s="3" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="O343" s="3" t="s">
         <v>859</v>
@@ -33971,7 +33977,7 @@
         <v>72</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="D344" s="3" t="s">
         <v>825</v>
@@ -34002,7 +34008,7 @@
         <v>50</v>
       </c>
       <c r="N344" s="3" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="O344" s="3" t="s">
         <v>1218</v>
@@ -34031,13 +34037,13 @@
     </row>
     <row r="345">
       <c r="A345" s="3" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="D345" s="3" t="s">
         <v>1104</v>
@@ -34071,7 +34077,7 @@
         <v>1120</v>
       </c>
       <c r="O345" s="3" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="P345" s="3" t="s">
         <v>175</v>
@@ -34097,13 +34103,13 @@
     </row>
     <row r="346">
       <c r="A346" s="3" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="D346" s="3" t="s">
         <v>1436</v>
@@ -34119,7 +34125,7 @@
         <v>385</v>
       </c>
       <c r="I346" s="3" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="J346" s="3" t="s">
         <v>1324</v>
@@ -34134,7 +34140,7 @@
         <v>32</v>
       </c>
       <c r="N346" s="3" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="O346" s="3" t="s">
         <v>1534</v>
@@ -34163,13 +34169,13 @@
     </row>
     <row r="347">
       <c r="A347" s="3" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C347" s="3" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="D347" s="3" t="s">
         <v>1439</v>
@@ -34200,7 +34206,7 @@
         <v>50</v>
       </c>
       <c r="N347" s="3" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="O347" s="3" t="s">
         <v>283</v>
@@ -34235,14 +34241,14 @@
         <v>23</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="E348" s="4"/>
       <c r="F348" s="3" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="G348" s="3" t="s">
         <v>62</v>
@@ -34266,10 +34272,10 @@
         <v>50</v>
       </c>
       <c r="N348" s="3" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="O348" s="3" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="P348" s="3" t="s">
         <v>454</v>
@@ -34295,20 +34301,20 @@
     </row>
     <row r="349">
       <c r="A349" s="3" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C349" s="3" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="E349" s="4"/>
       <c r="F349" s="3" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="G349" s="3" t="s">
         <v>27</v>
@@ -34317,7 +34323,7 @@
         <v>385</v>
       </c>
       <c r="I349" s="3" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="J349" s="3" t="s">
         <v>1358</v>
@@ -34361,20 +34367,20 @@
     </row>
     <row r="350">
       <c r="A350" s="3" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="B350" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="E350" s="4"/>
       <c r="F350" s="3" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="G350" s="3" t="s">
         <v>62</v>
@@ -34383,10 +34389,10 @@
         <v>385</v>
       </c>
       <c r="I350" s="3" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="J350" s="3" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="K350" s="3" t="s">
         <v>48</v>
@@ -34398,7 +34404,7 @@
         <v>50</v>
       </c>
       <c r="N350" s="3" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="O350" s="3" t="s">
         <v>1514</v>
@@ -34433,14 +34439,14 @@
         <v>23</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="E351" s="4"/>
       <c r="F351" s="3" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="G351" s="3" t="s">
         <v>87</v>
@@ -34461,7 +34467,7 @@
         <v>50</v>
       </c>
       <c r="N351" s="3" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="O351" s="3" t="s">
         <v>616</v>
@@ -34490,20 +34496,20 @@
     </row>
     <row r="352">
       <c r="A352" s="3" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="E352" s="4"/>
       <c r="F352" s="3" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="G352" s="3" t="s">
         <v>87</v>
@@ -34527,13 +34533,13 @@
         <v>50</v>
       </c>
       <c r="N352" s="3" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="O352" s="3" t="s">
         <v>99</v>
       </c>
       <c r="P352" s="3" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="Q352" s="3" t="s">
         <v>507</v>
@@ -34562,7 +34568,7 @@
         <v>23</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="D353" s="3" t="s">
         <v>1560</v>
@@ -34622,20 +34628,20 @@
     </row>
     <row r="354">
       <c r="A354" s="3" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="B354" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="E354" s="4"/>
       <c r="F354" s="3" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="G354" s="3" t="s">
         <v>172</v>
@@ -34688,13 +34694,13 @@
     </row>
     <row r="355">
       <c r="A355" s="3" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="B355" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="D355" s="3" t="s">
         <v>656</v>
@@ -34725,7 +34731,7 @@
         <v>50</v>
       </c>
       <c r="N355" s="3" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="O355" s="3" t="s">
         <v>785</v>
@@ -34760,14 +34766,14 @@
         <v>72</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="E356" s="4"/>
       <c r="F356" s="3" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="G356" s="3" t="s">
         <v>146</v>
@@ -34789,7 +34795,7 @@
         <v>50</v>
       </c>
       <c r="N356" s="3" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="O356" s="3" t="s">
         <v>37</v>
@@ -34818,20 +34824,20 @@
     </row>
     <row r="357">
       <c r="A357" s="3" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C357" s="3" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="E357" s="4"/>
       <c r="F357" s="3" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="G357" s="3" t="s">
         <v>146</v>
@@ -34881,20 +34887,20 @@
     </row>
     <row r="358">
       <c r="A358" s="3" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="B358" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="E358" s="4"/>
       <c r="F358" s="3" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="G358" s="3" t="s">
         <v>87</v>
@@ -34903,7 +34909,7 @@
         <v>385</v>
       </c>
       <c r="I358" s="3" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="J358" s="3" t="s">
         <v>116</v>
@@ -34921,7 +34927,7 @@
         <v>181</v>
       </c>
       <c r="O358" s="3" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="P358" s="3" t="s">
         <v>69</v>
@@ -34953,14 +34959,14 @@
         <v>23</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="E359" s="4"/>
       <c r="F359" s="3" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="G359" s="3" t="s">
         <v>27</v>
@@ -34984,7 +34990,7 @@
         <v>50</v>
       </c>
       <c r="N359" s="3" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="O359" s="3" t="s">
         <v>460</v>
@@ -35013,20 +35019,20 @@
     </row>
     <row r="360">
       <c r="A360" s="3" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="B360" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="E360" s="4"/>
       <c r="F360" s="3" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="G360" s="3" t="s">
         <v>154</v>
@@ -35079,20 +35085,20 @@
     </row>
     <row r="361">
       <c r="A361" s="3" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="B361" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="E361" s="4"/>
       <c r="F361" s="3" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="G361" s="3" t="s">
         <v>27</v>
@@ -35119,7 +35125,7 @@
         <v>531</v>
       </c>
       <c r="O361" s="3" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="P361" s="3" t="s">
         <v>285</v>
@@ -35151,14 +35157,14 @@
         <v>23</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="E362" s="4"/>
       <c r="F362" s="3" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="G362" s="3" t="s">
         <v>146</v>
@@ -35211,20 +35217,20 @@
     </row>
     <row r="363">
       <c r="A363" s="3" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="E363" s="4"/>
       <c r="F363" s="3" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="G363" s="3" t="s">
         <v>172</v>
@@ -35251,7 +35257,7 @@
         <v>1407</v>
       </c>
       <c r="O363" s="3" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="P363" s="3" t="s">
         <v>1232</v>
@@ -35277,20 +35283,20 @@
     </row>
     <row r="364">
       <c r="A364" s="3" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="B364" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="E364" s="4"/>
       <c r="F364" s="3" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="G364" s="3" t="s">
         <v>62</v>
@@ -35299,7 +35305,7 @@
         <v>385</v>
       </c>
       <c r="I364" s="3" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="J364" s="3" t="s">
         <v>64</v>
@@ -35349,14 +35355,14 @@
         <v>23</v>
       </c>
       <c r="C365" s="3" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="E365" s="4"/>
       <c r="F365" s="3" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="G365" s="3" t="s">
         <v>62</v>
@@ -35380,7 +35386,7 @@
         <v>50</v>
       </c>
       <c r="N365" s="3" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="O365" s="3" t="s">
         <v>544</v>
@@ -35409,20 +35415,20 @@
     </row>
     <row r="366">
       <c r="A366" s="3" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="B366" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C366" s="3" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="E366" s="4"/>
       <c r="F366" s="3" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="G366" s="3" t="s">
         <v>27</v>
@@ -35446,7 +35452,7 @@
         <v>50</v>
       </c>
       <c r="N366" s="3" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="O366" s="3" t="s">
         <v>472</v>
@@ -35481,14 +35487,14 @@
         <v>23</v>
       </c>
       <c r="C367" s="3" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="E367" s="4"/>
       <c r="F367" s="3" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="G367" s="3" t="s">
         <v>154</v>
@@ -35512,10 +35518,10 @@
         <v>50</v>
       </c>
       <c r="N367" s="3" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="O367" s="3" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="P367" s="3" t="s">
         <v>286</v>
@@ -35541,20 +35547,20 @@
     </row>
     <row r="368">
       <c r="A368" s="3" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="B368" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C368" s="3" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="E368" s="4"/>
       <c r="F368" s="3" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="G368" s="3" t="s">
         <v>62</v>
@@ -35578,10 +35584,10 @@
         <v>50</v>
       </c>
       <c r="N368" s="3" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="O368" s="3" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="P368" s="3" t="s">
         <v>507</v>
@@ -35607,13 +35613,13 @@
     </row>
     <row r="369">
       <c r="A369" s="3" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="B369" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C369" s="3" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="D369" s="3" t="s">
         <v>1594</v>
@@ -35676,7 +35682,7 @@
         <v>23</v>
       </c>
       <c r="C370" s="3" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="D370" s="3" t="s">
         <v>1493</v>
@@ -35707,7 +35713,7 @@
         <v>50</v>
       </c>
       <c r="N370" s="3" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="O370" s="3" t="s">
         <v>357</v>
@@ -35736,13 +35742,13 @@
     </row>
     <row r="371">
       <c r="A371" s="3" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="B371" s="3" t="s">
         <v>72</v>
       </c>
       <c r="C371" s="3" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D371" s="3" t="s">
         <v>290</v>
@@ -35800,13 +35806,13 @@
     </row>
     <row r="372">
       <c r="A372" s="3" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C372" s="3" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="D372" s="3" t="s">
         <v>1423</v>
@@ -35837,7 +35843,7 @@
         <v>32</v>
       </c>
       <c r="N372" s="3" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="O372" s="3" t="s">
         <v>140</v>
@@ -35872,7 +35878,7 @@
         <v>23</v>
       </c>
       <c r="C373" s="3" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="D373" s="3" t="s">
         <v>1418</v>
@@ -35888,7 +35894,7 @@
         <v>385</v>
       </c>
       <c r="I373" s="3" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="J373" s="3" t="s">
         <v>232</v>
@@ -35932,13 +35938,13 @@
     </row>
     <row r="374">
       <c r="A374" s="3" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="B374" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C374" s="3" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="D374" s="3" t="s">
         <v>1083</v>
@@ -35998,13 +36004,13 @@
     </row>
     <row r="375">
       <c r="A375" s="3" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B375" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C375" s="3" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="D375" s="3" t="s">
         <v>814</v>
@@ -36035,7 +36041,7 @@
         <v>395</v>
       </c>
       <c r="N375" s="3" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="O375" s="3" t="s">
         <v>1268</v>
@@ -36070,7 +36076,7 @@
         <v>23</v>
       </c>
       <c r="C376" s="3" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="D376" s="3" t="s">
         <v>753</v>
@@ -36101,10 +36107,10 @@
         <v>50</v>
       </c>
       <c r="N376" s="3" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="O376" s="3" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="P376" s="3" t="s">
         <v>1218</v>
@@ -36130,13 +36136,13 @@
     </row>
     <row r="377">
       <c r="A377" s="3" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B377" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C377" s="3" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="D377" s="3" t="s">
         <v>572</v>
@@ -36167,7 +36173,7 @@
         <v>50</v>
       </c>
       <c r="N377" s="3" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="O377" s="3" t="s">
         <v>66</v>
@@ -36196,20 +36202,20 @@
     </row>
     <row r="378">
       <c r="A378" s="3" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>72</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="E378" s="4"/>
       <c r="F378" s="3" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="G378" s="3" t="s">
         <v>146</v>
@@ -36262,20 +36268,20 @@
     </row>
     <row r="379">
       <c r="A379" s="3" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="B379" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C379" s="3" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="E379" s="4"/>
       <c r="F379" s="3" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="G379" s="3" t="s">
         <v>62</v>
@@ -36328,20 +36334,20 @@
     </row>
     <row r="380">
       <c r="A380" s="3" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C380" s="3" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="E380" s="4"/>
       <c r="F380" s="3" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="G380" s="3" t="s">
         <v>27</v>
@@ -36365,7 +36371,7 @@
         <v>50</v>
       </c>
       <c r="N380" s="3" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="O380" s="3" t="s">
         <v>34</v>
@@ -36394,20 +36400,20 @@
     </row>
     <row r="381">
       <c r="A381" s="3" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B381" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C381" s="3" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="E381" s="4"/>
       <c r="F381" s="3" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="G381" s="3" t="s">
         <v>172</v>
@@ -36434,7 +36440,7 @@
         <v>1407</v>
       </c>
       <c r="O381" s="3" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="P381" s="3" t="s">
         <v>1232</v>
@@ -36460,20 +36466,20 @@
     </row>
     <row r="382">
       <c r="A382" s="3" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="B382" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C382" s="3" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="E382" s="4"/>
       <c r="F382" s="3" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="G382" s="3" t="s">
         <v>172</v>
@@ -36523,20 +36529,20 @@
     </row>
     <row r="383">
       <c r="A383" s="3" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="B383" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C383" s="3" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="E383" s="4"/>
       <c r="F383" s="3" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="G383" s="3" t="s">
         <v>62</v>
@@ -36589,20 +36595,20 @@
     </row>
     <row r="384">
       <c r="A384" s="3" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="B384" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C384" s="3" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="E384" s="4"/>
       <c r="F384" s="3" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="G384" s="3" t="s">
         <v>62</v>
@@ -36655,20 +36661,20 @@
     </row>
     <row r="385">
       <c r="A385" s="3" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="B385" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C385" s="3" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="E385" s="4"/>
       <c r="F385" s="3" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="G385" s="3" t="s">
         <v>154</v>
@@ -36721,20 +36727,20 @@
     </row>
     <row r="386">
       <c r="A386" s="3" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="B386" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C386" s="3" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="E386" s="4"/>
       <c r="F386" s="3" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="G386" s="3" t="s">
         <v>146</v>
@@ -36758,7 +36764,7 @@
         <v>32</v>
       </c>
       <c r="N386" s="3" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="O386" s="3" t="s">
         <v>532</v>
@@ -36787,20 +36793,20 @@
     </row>
     <row r="387">
       <c r="A387" s="3" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B387" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C387" s="3" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="E387" s="4"/>
       <c r="F387" s="3" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="G387" s="3" t="s">
         <v>87</v>
@@ -36824,7 +36830,7 @@
         <v>50</v>
       </c>
       <c r="N387" s="3" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="O387" s="3" t="s">
         <v>828</v>
@@ -36853,20 +36859,20 @@
     </row>
     <row r="388">
       <c r="A388" s="3" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>72</v>
       </c>
       <c r="C388" s="3" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="E388" s="4"/>
       <c r="F388" s="3" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="G388" s="3" t="s">
         <v>172</v>
@@ -36875,7 +36881,7 @@
         <v>385</v>
       </c>
       <c r="I388" s="3" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="J388" s="3" t="s">
         <v>761</v>
@@ -36890,7 +36896,7 @@
         <v>50</v>
       </c>
       <c r="N388" s="3" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="O388" s="3" t="s">
         <v>1514</v>
@@ -36925,14 +36931,14 @@
         <v>23</v>
       </c>
       <c r="C389" s="3" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="E389" s="4"/>
       <c r="F389" s="3" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="G389" s="3" t="s">
         <v>87</v>
@@ -36959,7 +36965,7 @@
         <v>1566</v>
       </c>
       <c r="O389" s="3" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="P389" s="3" t="s">
         <v>683</v>
@@ -36985,13 +36991,13 @@
     </row>
     <row r="390">
       <c r="A390" s="3" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="B390" s="3" t="s">
         <v>72</v>
       </c>
       <c r="C390" s="3" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="D390" s="3" t="s">
         <v>429</v>
@@ -37022,7 +37028,7 @@
         <v>50</v>
       </c>
       <c r="N390" s="3" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="O390" s="3" t="s">
         <v>37</v>
@@ -37057,7 +37063,7 @@
         <v>23</v>
       </c>
       <c r="C391" s="3" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="D391" s="3" t="s">
         <v>759</v>
@@ -37103,7 +37109,7 @@
         <v>195</v>
       </c>
       <c r="S391" s="3" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="T391" s="3" t="s">
         <v>69</v>
@@ -37117,13 +37123,13 @@
     </row>
     <row r="392">
       <c r="A392" s="3" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="B392" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C392" s="3" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="D392" s="3" t="s">
         <v>716</v>
@@ -37154,7 +37160,7 @@
         <v>778</v>
       </c>
       <c r="O392" s="3" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="P392" s="3" t="s">
         <v>499</v>
@@ -37186,7 +37192,7 @@
         <v>72</v>
       </c>
       <c r="C393" s="3" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="D393" s="3" t="s">
         <v>105</v>
@@ -37217,10 +37223,10 @@
         <v>50</v>
       </c>
       <c r="N393" s="3" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="O393" s="3" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="P393" s="3" t="s">
         <v>917</v>
@@ -37252,7 +37258,7 @@
         <v>23</v>
       </c>
       <c r="C394" s="3" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="D394" s="3" t="s">
         <v>1063</v>
@@ -37283,7 +37289,7 @@
         <v>50</v>
       </c>
       <c r="N394" s="3" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="O394" s="3" t="s">
         <v>585</v>
@@ -37312,13 +37318,13 @@
     </row>
     <row r="395">
       <c r="A395" s="3" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="B395" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C395" s="3" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="D395" s="3" t="s">
         <v>1564</v>
@@ -37349,7 +37355,7 @@
         <v>50</v>
       </c>
       <c r="N395" s="3" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="O395" s="3" t="s">
         <v>37</v>
@@ -37384,7 +37390,7 @@
         <v>23</v>
       </c>
       <c r="C396" s="3" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="D396" s="3" t="s">
         <v>1161</v>
@@ -37412,7 +37418,7 @@
         <v>50</v>
       </c>
       <c r="N396" s="3" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="O396" s="3" t="s">
         <v>1167</v>
@@ -37441,20 +37447,20 @@
     </row>
     <row r="397">
       <c r="A397" s="3" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B397" s="3" t="s">
         <v>72</v>
       </c>
       <c r="C397" s="3" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="E397" s="4"/>
       <c r="F397" s="3" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="G397" s="3" t="s">
         <v>146</v>
@@ -37475,7 +37481,7 @@
         <v>50</v>
       </c>
       <c r="N397" s="3" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="O397" s="3" t="s">
         <v>438</v>
@@ -37504,20 +37510,20 @@
     </row>
     <row r="398">
       <c r="A398" s="3" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="B398" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C398" s="3" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="E398" s="4"/>
       <c r="F398" s="3" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="G398" s="3" t="s">
         <v>62</v>
@@ -37574,14 +37580,14 @@
         <v>23</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="E399" s="4"/>
       <c r="F399" s="3" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="G399" s="3" t="s">
         <v>146</v>
@@ -37590,7 +37596,7 @@
         <v>385</v>
       </c>
       <c r="I399" s="3" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="K399" s="3" t="s">
         <v>48</v>
@@ -37602,7 +37608,7 @@
         <v>32</v>
       </c>
       <c r="N399" s="3" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="O399" s="3" t="s">
         <v>1315</v>
@@ -37637,14 +37643,14 @@
         <v>23</v>
       </c>
       <c r="C400" s="3" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="E400" s="4"/>
       <c r="F400" s="3" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="G400" s="3" t="s">
         <v>87</v>
@@ -37665,7 +37671,7 @@
         <v>50</v>
       </c>
       <c r="N400" s="3" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="O400" s="3" t="s">
         <v>1469</v>
@@ -37700,14 +37706,14 @@
         <v>23</v>
       </c>
       <c r="C401" s="3" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="E401" s="4"/>
       <c r="F401" s="3" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="G401" s="3" t="s">
         <v>27</v>
@@ -37731,10 +37737,10 @@
         <v>50</v>
       </c>
       <c r="N401" s="3" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="O401" s="3" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="P401" s="3" t="s">
         <v>250</v>
@@ -37760,20 +37766,20 @@
     </row>
     <row r="402">
       <c r="A402" s="3" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="B402" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C402" s="3" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="E402" s="4"/>
       <c r="F402" s="3" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="G402" s="3" t="s">
         <v>27</v>
@@ -37797,7 +37803,7 @@
         <v>50</v>
       </c>
       <c r="N402" s="3" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="O402" s="3" t="s">
         <v>34</v>
@@ -37832,7 +37838,7 @@
         <v>72</v>
       </c>
       <c r="C403" s="3" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="D403" s="3" t="s">
         <v>215</v>
@@ -37895,7 +37901,7 @@
         <v>23</v>
       </c>
       <c r="C404" s="3" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="D404" s="3" t="s">
         <v>1466</v>
@@ -37955,13 +37961,13 @@
     </row>
     <row r="405">
       <c r="A405" s="3" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="B405" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C405" s="3" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="D405" s="3" t="s">
         <v>1475</v>
@@ -38027,14 +38033,14 @@
         <v>23</v>
       </c>
       <c r="C406" s="3" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="E406" s="4"/>
       <c r="F406" s="3" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="G406" s="3" t="s">
         <v>27</v>
@@ -38055,7 +38061,7 @@
         <v>50</v>
       </c>
       <c r="N406" s="3" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="O406" s="3" t="s">
         <v>227</v>
@@ -38090,14 +38096,14 @@
         <v>23</v>
       </c>
       <c r="C407" s="3" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="D407" s="3" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="E407" s="4"/>
       <c r="F407" s="3" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="G407" s="3" t="s">
         <v>87</v>
@@ -38150,20 +38156,20 @@
     </row>
     <row r="408">
       <c r="A408" s="3" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="B408" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C408" s="3" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="E408" s="4"/>
       <c r="F408" s="3" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="G408" s="3" t="s">
         <v>27</v>
@@ -38216,13 +38222,13 @@
     </row>
     <row r="409">
       <c r="A409" s="3" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="B409" s="3" t="s">
         <v>72</v>
       </c>
       <c r="C409" s="3" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="D409" s="3" t="s">
         <v>198</v>
@@ -38285,7 +38291,7 @@
         <v>23</v>
       </c>
       <c r="C410" s="3" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="D410" s="3" t="s">
         <v>170</v>
@@ -38316,7 +38322,7 @@
         <v>50</v>
       </c>
       <c r="N410" s="3" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="O410" s="3" t="s">
         <v>828</v>
@@ -38345,13 +38351,13 @@
     </row>
     <row r="411">
       <c r="A411" s="3" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="B411" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C411" s="3" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="D411" s="3" t="s">
         <v>457</v>
@@ -38379,10 +38385,10 @@
         <v>50</v>
       </c>
       <c r="N411" s="3" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="O411" s="3" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="P411" s="3" t="s">
         <v>1169</v>
@@ -38408,13 +38414,13 @@
     </row>
     <row r="412">
       <c r="A412" s="3" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="B412" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C412" s="3" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="D412" s="3" t="s">
         <v>528</v>
@@ -38448,7 +38454,7 @@
         <v>858</v>
       </c>
       <c r="O412" s="3" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="P412" s="3" t="s">
         <v>439</v>
@@ -38469,7 +38475,7 @@
         <v>92</v>
       </c>
       <c r="V412" s="3" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="413">
@@ -38480,14 +38486,14 @@
         <v>23</v>
       </c>
       <c r="C413" s="3" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="D413" s="3" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="E413" s="4"/>
       <c r="F413" s="3" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="G413" s="3" t="s">
         <v>172</v>
@@ -38511,7 +38517,7 @@
         <v>50</v>
       </c>
       <c r="N413" s="3" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="O413" s="3" t="s">
         <v>37</v>
@@ -38546,14 +38552,14 @@
         <v>23</v>
       </c>
       <c r="C414" s="3" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="D414" s="3" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="E414" s="4"/>
       <c r="F414" s="3" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="G414" s="3" t="s">
         <v>87</v>
@@ -38574,7 +38580,7 @@
         <v>50</v>
       </c>
       <c r="N414" s="3" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="O414" s="3" t="s">
         <v>557</v>
@@ -38603,20 +38609,20 @@
     </row>
     <row r="415">
       <c r="A415" s="3" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="B415" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C415" s="3" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="D415" s="3" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="E415" s="4"/>
       <c r="F415" s="3" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="G415" s="3" t="s">
         <v>154</v>
@@ -38643,7 +38649,7 @@
         <v>1332</v>
       </c>
       <c r="O415" s="3" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="P415" s="3" t="s">
         <v>1169</v>
@@ -38669,20 +38675,20 @@
     </row>
     <row r="416">
       <c r="A416" s="3" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="B416" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C416" s="3" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="D416" s="3" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="E416" s="4"/>
       <c r="F416" s="3" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="G416" s="3" t="s">
         <v>172</v>
@@ -38741,14 +38747,14 @@
         <v>23</v>
       </c>
       <c r="C417" s="3" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="E417" s="4"/>
       <c r="F417" s="3" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="G417" s="3" t="s">
         <v>146</v>
@@ -38801,20 +38807,20 @@
     </row>
     <row r="418">
       <c r="A418" s="3" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C418" s="3" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="D418" s="3" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="E418" s="4"/>
       <c r="F418" s="3" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="G418" s="3" t="s">
         <v>62</v>
@@ -38838,7 +38844,7 @@
         <v>50</v>
       </c>
       <c r="N418" s="3" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="O418" s="3" t="s">
         <v>1335</v>
@@ -38867,13 +38873,13 @@
     </row>
     <row r="419">
       <c r="A419" s="3" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C419" s="3" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="D419" s="3" t="s">
         <v>187</v>
@@ -38937,14 +38943,14 @@
         <v>23</v>
       </c>
       <c r="C420" s="3" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="E420" s="4"/>
       <c r="F420" s="3" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="G420" s="3" t="s">
         <v>172</v>
@@ -39003,14 +39009,14 @@
         <v>23</v>
       </c>
       <c r="C421" s="3" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="E421" s="4"/>
       <c r="F421" s="3" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="G421" s="3" t="s">
         <v>154</v>
@@ -39034,7 +39040,7 @@
         <v>50</v>
       </c>
       <c r="N421" s="3" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="O421" s="3" t="s">
         <v>635</v>
@@ -39063,13 +39069,13 @@
     </row>
     <row r="422">
       <c r="A422" s="3" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C422" s="3" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="D422" s="3" t="s">
         <v>223</v>
@@ -39098,7 +39104,7 @@
         <v>32</v>
       </c>
       <c r="N422" s="3" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="O422" s="3" t="s">
         <v>1176</v>
@@ -39133,14 +39139,14 @@
         <v>23</v>
       </c>
       <c r="C423" s="3" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="D423" s="3" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="E423" s="4"/>
       <c r="F423" s="3" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="G423" s="3" t="s">
         <v>154</v>
@@ -39164,7 +39170,7 @@
         <v>50</v>
       </c>
       <c r="N423" s="3" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="O423" s="3" t="s">
         <v>227</v>
@@ -39199,7 +39205,7 @@
         <v>23</v>
       </c>
       <c r="C424" s="3" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="D424" s="3" t="s">
         <v>942</v>
@@ -39230,7 +39236,7 @@
         <v>50</v>
       </c>
       <c r="N424" s="3" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="O424" s="3" t="s">
         <v>779</v>
@@ -39259,20 +39265,20 @@
     </row>
     <row r="425">
       <c r="A425" s="3" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C425" s="3" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="E425" s="4"/>
       <c r="F425" s="3" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="G425" s="3" t="s">
         <v>87</v>
@@ -39296,10 +39302,10 @@
         <v>50</v>
       </c>
       <c r="N425" s="3" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="O425" s="3" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="P425" s="3" t="s">
         <v>665</v>
@@ -39325,13 +39331,13 @@
     </row>
     <row r="426">
       <c r="A426" s="3" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C426" s="3" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="D426" s="3" t="s">
         <v>925</v>
@@ -39359,7 +39365,7 @@
         <v>50</v>
       </c>
       <c r="N426" s="3" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="O426" s="3" t="s">
         <v>713</v>
@@ -39394,14 +39400,14 @@
         <v>23</v>
       </c>
       <c r="C427" s="3" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="D427" s="3" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="E427" s="4"/>
       <c r="F427" s="3" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="G427" s="3" t="s">
         <v>87</v>
@@ -39460,14 +39466,14 @@
         <v>23</v>
       </c>
       <c r="C428" s="3" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="D428" s="3" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="E428" s="4"/>
       <c r="F428" s="3" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="G428" s="3" t="s">
         <v>87</v>
@@ -39491,10 +39497,10 @@
         <v>50</v>
       </c>
       <c r="N428" s="3" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="O428" s="3" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="P428" s="3" t="s">
         <v>507</v>
@@ -39520,20 +39526,20 @@
     </row>
     <row r="429">
       <c r="A429" s="3" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C429" s="3" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="D429" s="3" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="E429" s="4"/>
       <c r="F429" s="3" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="G429" s="3" t="s">
         <v>172</v>
@@ -39557,7 +39563,7 @@
         <v>50</v>
       </c>
       <c r="N429" s="3" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="O429" s="3" t="s">
         <v>1046</v>
@@ -39592,14 +39598,14 @@
         <v>72</v>
       </c>
       <c r="C430" s="3" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="E430" s="4"/>
       <c r="F430" s="3" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="G430" s="3" t="s">
         <v>62</v>
@@ -39652,20 +39658,20 @@
     </row>
     <row r="431">
       <c r="A431" s="3" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C431" s="3" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="D431" s="3" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="E431" s="4"/>
       <c r="F431" s="3" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="G431" s="3" t="s">
         <v>154</v>
@@ -39718,13 +39724,13 @@
     </row>
     <row r="432">
       <c r="A432" s="3" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>72</v>
       </c>
       <c r="C432" s="3" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="D432" s="3" t="s">
         <v>1607</v>
@@ -39784,13 +39790,13 @@
     </row>
     <row r="433">
       <c r="A433" s="3" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C433" s="3" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="D433" s="3" t="s">
         <v>1602</v>
@@ -39821,7 +39827,7 @@
         <v>50</v>
       </c>
       <c r="N433" s="3" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="O433" s="3" t="s">
         <v>1116</v>
@@ -39850,13 +39856,13 @@
     </row>
     <row r="434">
       <c r="A434" s="3" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C434" s="3" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="D434" s="3" t="s">
         <v>1560</v>
@@ -39922,14 +39928,14 @@
         <v>23</v>
       </c>
       <c r="C435" s="3" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="D435" s="3" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="E435" s="4"/>
       <c r="F435" s="3" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="G435" s="3" t="s">
         <v>172</v>
@@ -39953,7 +39959,7 @@
         <v>50</v>
       </c>
       <c r="N435" s="3" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="O435" s="3" t="s">
         <v>472</v>
@@ -39982,20 +39988,20 @@
     </row>
     <row r="436">
       <c r="A436" s="3" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B436" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C436" s="3" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="D436" s="3" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="E436" s="4"/>
       <c r="F436" s="3" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="G436" s="3" t="s">
         <v>146</v>
@@ -40019,10 +40025,10 @@
         <v>50</v>
       </c>
       <c r="N436" s="3" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="O436" s="3" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="P436" s="3" t="s">
         <v>219</v>
@@ -40054,7 +40060,7 @@
         <v>72</v>
       </c>
       <c r="C437" s="3" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D437" s="3" t="s">
         <v>693</v>
@@ -40120,7 +40126,7 @@
         <v>23</v>
       </c>
       <c r="C438" s="3" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D438" s="3" t="s">
         <v>306</v>
@@ -40151,7 +40157,7 @@
         <v>32</v>
       </c>
       <c r="N438" s="3" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="O438" s="3" t="s">
         <v>1530</v>
@@ -40180,13 +40186,13 @@
     </row>
     <row r="439">
       <c r="A439" s="3" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C439" s="3" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D439" s="3" t="s">
         <v>1230</v>
@@ -40244,13 +40250,13 @@
     </row>
     <row r="440">
       <c r="A440" s="3" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C440" s="3" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D440" s="3" t="s">
         <v>1511</v>
@@ -40281,7 +40287,7 @@
         <v>50</v>
       </c>
       <c r="N440" s="3" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="O440" s="3" t="s">
         <v>1001</v>
@@ -40316,14 +40322,14 @@
         <v>23</v>
       </c>
       <c r="C441" s="3" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D441" s="3" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E441" s="4"/>
       <c r="F441" s="3" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="G441" s="3" t="s">
         <v>62</v>
@@ -40345,7 +40351,7 @@
         <v>50</v>
       </c>
       <c r="N441" s="3" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="O441" s="3" t="s">
         <v>1409</v>
@@ -40380,14 +40386,14 @@
         <v>23</v>
       </c>
       <c r="C442" s="3" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D442" s="3" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E442" s="4"/>
       <c r="F442" s="3" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="G442" s="3" t="s">
         <v>146</v>
@@ -40409,10 +40415,10 @@
         <v>50</v>
       </c>
       <c r="N442" s="3" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="O442" s="3" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="P442" s="3" t="s">
         <v>507</v>
@@ -40438,20 +40444,20 @@
     </row>
     <row r="443">
       <c r="A443" s="3" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C443" s="3" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="D443" s="3" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="E443" s="4"/>
       <c r="F443" s="3" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="G443" s="3" t="s">
         <v>62</v>
@@ -40478,7 +40484,7 @@
         <v>1328</v>
       </c>
       <c r="O443" s="3" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="P443" s="3" t="s">
         <v>1002</v>
@@ -40504,13 +40510,13 @@
     </row>
     <row r="444">
       <c r="A444" s="3" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>72</v>
       </c>
       <c r="C444" s="3" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="D444" s="3" t="s">
         <v>144</v>
@@ -40568,13 +40574,13 @@
     </row>
     <row r="445">
       <c r="A445" s="3" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C445" s="3" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="D445" s="3" t="s">
         <v>1394</v>
@@ -40605,7 +40611,7 @@
         <v>50</v>
       </c>
       <c r="N445" s="3" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="O445" s="3" t="s">
         <v>610</v>
@@ -40634,13 +40640,13 @@
     </row>
     <row r="446">
       <c r="A446" s="3" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C446" s="3" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="D446" s="3" t="s">
         <v>572</v>
@@ -40700,13 +40706,13 @@
     </row>
     <row r="447">
       <c r="A447" s="3" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C447" s="3" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="D447" s="3" t="s">
         <v>1018</v>
@@ -40737,7 +40743,7 @@
         <v>50</v>
       </c>
       <c r="N447" s="3" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="O447" s="3" t="s">
         <v>1139</v>
@@ -40766,20 +40772,20 @@
     </row>
     <row r="448">
       <c r="A448" s="3" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C448" s="3" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="D448" s="3" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="E448" s="4"/>
       <c r="F448" s="3" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="G448" s="3" t="s">
         <v>172</v>
@@ -40804,7 +40810,7 @@
         <v>459</v>
       </c>
       <c r="O448" s="3" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="P448" s="3" t="s">
         <v>996</v>
@@ -40836,14 +40842,14 @@
         <v>23</v>
       </c>
       <c r="C449" s="3" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="D449" s="3" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="E449" s="4"/>
       <c r="F449" s="3" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="G449" s="3" t="s">
         <v>154</v>
@@ -40870,7 +40876,7 @@
         <v>974</v>
       </c>
       <c r="O449" s="3" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="P449" s="3" t="s">
         <v>883</v>
@@ -40896,20 +40902,20 @@
     </row>
     <row r="450">
       <c r="A450" s="3" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C450" s="3" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="D450" s="3" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="E450" s="4"/>
       <c r="F450" s="3" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="G450" s="3" t="s">
         <v>172</v>
@@ -40962,20 +40968,20 @@
     </row>
     <row r="451">
       <c r="A451" s="3" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C451" s="3" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="D451" s="3" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="E451" s="4"/>
       <c r="F451" s="3" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="G451" s="3" t="s">
         <v>62</v>
@@ -40999,10 +41005,10 @@
         <v>50</v>
       </c>
       <c r="N451" s="3" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="O451" s="3" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="P451" s="3" t="s">
         <v>294</v>
@@ -41034,14 +41040,14 @@
         <v>23</v>
       </c>
       <c r="C452" s="3" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="D452" s="3" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="E452" s="4"/>
       <c r="F452" s="3" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="G452" s="3" t="s">
         <v>154</v>
@@ -41065,10 +41071,10 @@
         <v>50</v>
       </c>
       <c r="N452" s="3" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="O452" s="3" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="P452" s="3" t="s">
         <v>1169</v>
@@ -41103,11 +41109,11 @@
         <v>24</v>
       </c>
       <c r="D453" s="3" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="E453" s="4"/>
       <c r="F453" s="3" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="G453" s="3" t="s">
         <v>27</v>
@@ -41185,23 +41191,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="B3" s="3">
         <v>452</v>
@@ -41212,23 +41218,23 @@
         <v>5</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
     </row>
   </sheetData>

--- a/魔物娘TD_名字编号属性对照表.xlsx
+++ b/魔物娘TD_名字编号属性对照表.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9853" uniqueCount="2469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2531" uniqueCount="2531">
   <si>
     <t>编号</t>
   </si>
@@ -7443,6 +7443,192 @@
   </si>
   <si>
     <t>编号、稀有度、种族名、日文名、属性、初期职业、武器、类型、攻击类型、配置类型、移动类型及基础属性</t>
+  </si>
+  <si>
+    <t>469</t>
+  </si>
+  <si>
+    <t>バエル娘</t>
+  </si>
+  <si>
+    <t>15 / 魔法剣</t>
+  </si>
+  <si>
+    <t>悪魔/進化</t>
+  </si>
+  <si>
+    <t>2166</t>
+  </si>
+  <si>
+    <t>468</t>
+  </si>
+  <si>
+    <t>フェネクス娘</t>
+  </si>
+  <si>
+    <t>43 / ブーメラン</t>
+  </si>
+  <si>
+    <t>1764</t>
+  </si>
+  <si>
+    <t>467</t>
+  </si>
+  <si>
+    <t>ライトニンググリフォン娘</t>
+  </si>
+  <si>
+    <t>魔獣/進化</t>
+  </si>
+  <si>
+    <t>1506</t>
+  </si>
+  <si>
+    <t>ベルグリシ娘</t>
+  </si>
+  <si>
+    <t>デミ/進化</t>
+  </si>
+  <si>
+    <t>4485</t>
+  </si>
+  <si>
+    <t>夜戯のアラクネ娘</t>
+  </si>
+  <si>
+    <t>1508</t>
+  </si>
+  <si>
+    <t>魔戯猫グリマルキン娘</t>
+  </si>
+  <si>
+    <t>魔獣</t>
+  </si>
+  <si>
+    <t>2185</t>
+  </si>
+  <si>
+    <t>463</t>
+  </si>
+  <si>
+    <t>戯触のローパー娘</t>
+  </si>
+  <si>
+    <t>462</t>
+  </si>
+  <si>
+    <t>ハッグ娘</t>
+  </si>
+  <si>
+    <t>ドルゼフィーダ</t>
+  </si>
+  <si>
+    <t>461</t>
+  </si>
+  <si>
+    <t>ティアマト娘</t>
+  </si>
+  <si>
+    <t>ティアマリア</t>
+  </si>
+  <si>
+    <t>ドラゴン/海魔/禁忌</t>
+  </si>
+  <si>
+    <t>2356</t>
+  </si>
+  <si>
+    <t>598</t>
+  </si>
+  <si>
+    <t>プロメテウス娘</t>
+  </si>
+  <si>
+    <t>メテリナ</t>
+  </si>
+  <si>
+    <t>デミ/禁忌</t>
+  </si>
+  <si>
+    <t>459</t>
+  </si>
+  <si>
+    <t>フェンリル娘</t>
+  </si>
+  <si>
+    <t>エリル</t>
+  </si>
+  <si>
+    <t>魔獣/禁忌</t>
+  </si>
+  <si>
+    <t>禁忌の神殿</t>
+  </si>
+  <si>
+    <t>458</t>
+  </si>
+  <si>
+    <t>ワーキャット娘</t>
+  </si>
+  <si>
+    <t>ミャルナ</t>
+  </si>
+  <si>
+    <t>デミ/魔獣</t>
+  </si>
+  <si>
+    <t>457</t>
+  </si>
+  <si>
+    <t>T.O.W.E.R.typeM</t>
+  </si>
+  <si>
+    <t>ティヴェル</t>
+  </si>
+  <si>
+    <t>456</t>
+  </si>
+  <si>
+    <t>コズミックモーフ娘</t>
+  </si>
+  <si>
+    <t>ヴォミラ</t>
+  </si>
+  <si>
+    <t>1490</t>
+  </si>
+  <si>
+    <t>フライング・ヒューマノイド娘</t>
+  </si>
+  <si>
+    <t>シエルナ</t>
+  </si>
+  <si>
+    <t>454</t>
+  </si>
+  <si>
+    <t>ヴィーナシアン娘</t>
+  </si>
+  <si>
+    <t>ルキーナ</t>
+  </si>
+  <si>
+    <t>3905</t>
+  </si>
+  <si>
+    <t>453</t>
+  </si>
+  <si>
+    <t>ケルピー娘</t>
+  </si>
+  <si>
+    <t>ストリオーネ</t>
+  </si>
+  <si>
+    <t>1107</t>
+  </si>
+  <si>
+    <t>進化</t>
   </si>
 </sst>
 </file>
@@ -8335,7 +8521,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:V453"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
@@ -8551,6 +8737,9 @@
       <c r="V3" t="s">
         <v>42</v>
       </c>
+      <c r="J3" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" t="s">
@@ -8752,6 +8941,9 @@
       <c r="V6" t="s">
         <v>42</v>
       </c>
+      <c r="J6" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" t="s">
@@ -9157,6 +9349,9 @@
       <c r="V12" t="s">
         <v>42</v>
       </c>
+      <c r="J12" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" t="s">
@@ -9494,6 +9689,9 @@
       <c r="V17" t="s">
         <v>42</v>
       </c>
+      <c r="J17" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" t="s">
@@ -9757,6 +9955,9 @@
       <c r="V21" t="s">
         <v>42</v>
       </c>
+      <c r="J21" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="22" spans="1:22">
       <c r="A22" t="s">
@@ -9890,6 +10091,9 @@
       <c r="V23" t="s">
         <v>42</v>
       </c>
+      <c r="J23" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="24" spans="1:22">
       <c r="A24" t="s">
@@ -10620,6 +10824,9 @@
       <c r="V34" t="s">
         <v>42</v>
       </c>
+      <c r="J34" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="35" spans="1:22">
       <c r="A35" t="s">
@@ -11084,6 +11291,9 @@
       <c r="V41" t="s">
         <v>42</v>
       </c>
+      <c r="J41" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" t="s">
@@ -11616,6 +11826,9 @@
       <c r="V49" t="s">
         <v>494</v>
       </c>
+      <c r="J49" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="50" spans="1:22">
       <c r="A50" t="s">
@@ -11749,6 +11962,9 @@
       <c r="V51" t="s">
         <v>494</v>
       </c>
+      <c r="J51" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="52" spans="1:22">
       <c r="A52" t="s">
@@ -11879,6 +12095,9 @@
       <c r="V53" t="s">
         <v>42</v>
       </c>
+      <c r="J53" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="54" spans="1:22">
       <c r="A54" t="s">
@@ -12012,6 +12231,9 @@
       <c r="V55" t="s">
         <v>42</v>
       </c>
+      <c r="J55" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="56" spans="1:22">
       <c r="A56" t="s">
@@ -12275,6 +12497,9 @@
       <c r="V59" t="s">
         <v>42</v>
       </c>
+      <c r="J59" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="60" spans="1:22">
       <c r="A60" t="s">
@@ -12538,6 +12763,9 @@
       <c r="V63" t="s">
         <v>42</v>
       </c>
+      <c r="J63" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="64" spans="1:22">
       <c r="A64" t="s">
@@ -12603,6 +12831,9 @@
       <c r="V64" t="s">
         <v>42</v>
       </c>
+      <c r="J64" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="65" spans="1:22">
       <c r="A65" t="s">
@@ -12804,6 +13035,9 @@
       <c r="V67" t="s">
         <v>42</v>
       </c>
+      <c r="J67" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="68" spans="1:22">
       <c r="A68" t="s">
@@ -12869,6 +13103,9 @@
       <c r="V68" t="s">
         <v>494</v>
       </c>
+      <c r="J68" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="69" spans="1:22">
       <c r="A69" t="s">
@@ -13002,6 +13239,9 @@
       <c r="V70" t="s">
         <v>42</v>
       </c>
+      <c r="J70" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="71" spans="1:22">
       <c r="A71" t="s">
@@ -13868,6 +14108,9 @@
       <c r="V83" t="s">
         <v>42</v>
       </c>
+      <c r="J83" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="84" spans="1:22">
       <c r="A84" t="s">
@@ -14069,6 +14312,9 @@
       <c r="V86" t="s">
         <v>42</v>
       </c>
+      <c r="J86" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="87" spans="1:22">
       <c r="A87" t="s">
@@ -14134,6 +14380,9 @@
       <c r="V87" t="s">
         <v>42</v>
       </c>
+      <c r="J87" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="88" spans="1:22">
       <c r="A88" t="s">
@@ -14403,6 +14652,9 @@
       <c r="V91" t="s">
         <v>42</v>
       </c>
+      <c r="J91" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="92" spans="1:22">
       <c r="A92" t="s">
@@ -14604,6 +14856,9 @@
       <c r="V94" t="s">
         <v>42</v>
       </c>
+      <c r="J94" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="95" spans="1:22">
       <c r="A95" t="s">
@@ -15331,6 +15586,9 @@
       <c r="V105" t="s">
         <v>494</v>
       </c>
+      <c r="J105" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="106" spans="1:22">
       <c r="A106" t="s">
@@ -16132,6 +16390,9 @@
       <c r="V117" t="s">
         <v>494</v>
       </c>
+      <c r="J117" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="118" spans="1:22">
       <c r="A118" t="s">
@@ -17409,6 +17670,9 @@
       <c r="V136" t="s">
         <v>1041</v>
       </c>
+      <c r="J136" t="s">
+        <v>2480</v>
+      </c>
     </row>
     <row r="137" spans="1:22">
       <c r="A137" t="s">
@@ -20658,6 +20922,9 @@
       <c r="V184" t="s">
         <v>494</v>
       </c>
+      <c r="J184" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="185" spans="1:22">
       <c r="A185" t="s">
@@ -20791,6 +21058,9 @@
       <c r="V186" t="s">
         <v>1041</v>
       </c>
+      <c r="J186" t="s">
+        <v>2530</v>
+      </c>
     </row>
     <row r="187" spans="1:22">
       <c r="A187" t="s">
@@ -21193,6 +21463,9 @@
       <c r="V192" t="s">
         <v>494</v>
       </c>
+      <c r="J192" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="193" spans="1:22">
       <c r="A193" t="s">
@@ -21326,6 +21599,9 @@
       <c r="V194" t="s">
         <v>42</v>
       </c>
+      <c r="J194" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="195" spans="1:22">
       <c r="A195" t="s">
@@ -22003,6 +22279,9 @@
       <c r="V204" t="s">
         <v>42</v>
       </c>
+      <c r="J204" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="205" spans="1:22">
       <c r="A205" t="s">
@@ -23954,6 +24233,9 @@
       <c r="V233" t="s">
         <v>42</v>
       </c>
+      <c r="J233" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="234" spans="1:22">
       <c r="A234" t="s">
@@ -24291,6 +24573,9 @@
       <c r="V238" t="s">
         <v>966</v>
       </c>
+      <c r="J238" t="s">
+        <v>2530</v>
+      </c>
     </row>
     <row r="239" spans="1:22">
       <c r="A239" t="s">
@@ -24560,6 +24845,9 @@
       <c r="V242" t="s">
         <v>494</v>
       </c>
+      <c r="J242" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="243" spans="1:22">
       <c r="A243" t="s">
@@ -26452,6 +26740,9 @@
       <c r="V270" t="s">
         <v>42</v>
       </c>
+      <c r="J270" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="271" spans="1:22">
       <c r="A271" t="s">
@@ -27401,6 +27692,9 @@
       <c r="V284" t="s">
         <v>1041</v>
       </c>
+      <c r="J284" t="s">
+        <v>2530</v>
+      </c>
     </row>
     <row r="285" spans="1:22">
       <c r="A285" t="s">
@@ -27466,6 +27760,9 @@
       <c r="V285" t="s">
         <v>1041</v>
       </c>
+      <c r="J285" t="s">
+        <v>2530</v>
+      </c>
     </row>
     <row r="286" spans="1:22">
       <c r="A286" t="s">
@@ -28551,6 +28848,9 @@
       <c r="V301" t="s">
         <v>42</v>
       </c>
+      <c r="J301" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="302" spans="1:22">
       <c r="A302" t="s">
@@ -30295,6 +30595,9 @@
       <c r="V327" t="s">
         <v>494</v>
       </c>
+      <c r="J327" t="s">
+        <v>2530</v>
+      </c>
     </row>
     <row r="328" spans="1:22">
       <c r="A328" t="s">
@@ -30972,6 +31275,9 @@
       <c r="V337" t="s">
         <v>42</v>
       </c>
+      <c r="J337" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="338" spans="1:22">
       <c r="A338" t="s">
@@ -32258,6 +32564,9 @@
       <c r="V356" t="s">
         <v>494</v>
       </c>
+      <c r="J356" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="357" spans="1:22">
       <c r="A357" t="s">
@@ -34691,6 +35000,9 @@
       <c r="V392" t="s">
         <v>42</v>
       </c>
+      <c r="J392" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="393" spans="1:22">
       <c r="A393" t="s">
@@ -35025,6 +35337,9 @@
       <c r="V397" t="s">
         <v>1553</v>
       </c>
+      <c r="J397" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="398" spans="1:22">
       <c r="A398" t="s">
@@ -35220,6 +35535,9 @@
       <c r="V400" t="s">
         <v>966</v>
       </c>
+      <c r="J400" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="401" spans="1:22">
       <c r="A401" t="s">
@@ -35622,6 +35940,9 @@
       <c r="V406" t="s">
         <v>42</v>
       </c>
+      <c r="J406" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="407" spans="1:22">
       <c r="A407" t="s">
@@ -35956,6 +36277,9 @@
       <c r="V411" t="s">
         <v>42</v>
       </c>
+      <c r="J411" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="412" spans="1:22">
       <c r="A412" t="s">
@@ -36157,6 +36481,9 @@
       <c r="V414" t="s">
         <v>555</v>
       </c>
+      <c r="J414" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="415" spans="1:22">
       <c r="A415" t="s">
@@ -36494,6 +36821,9 @@
       <c r="V419" t="s">
         <v>555</v>
       </c>
+      <c r="J419" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="420" spans="1:22">
       <c r="A420" t="s">
@@ -36695,6 +37025,9 @@
       <c r="V422" t="s">
         <v>966</v>
       </c>
+      <c r="J422" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="423" spans="1:22">
       <c r="A423" t="s">
@@ -36964,6 +37297,9 @@
       <c r="V426" t="s">
         <v>966</v>
       </c>
+      <c r="J426" t="s">
+        <v>2530</v>
+      </c>
     </row>
     <row r="427" ht="19.5" customHeight="1" spans="1:22">
       <c r="A427" t="s">
@@ -38043,6 +38379,9 @@
       <c r="V442" t="s">
         <v>42</v>
       </c>
+      <c r="J442" t="s">
+        <v>2488</v>
+      </c>
     </row>
     <row r="443" spans="1:22">
       <c r="A443" t="s">
@@ -38786,8 +39125,1056 @@
         <v>966</v>
       </c>
     </row>
+    <row r="454" spans="1:22">
+      <c r="A454" t="s">
+        <v>2469</v>
+      </c>
+      <c r="B454" t="s">
+        <v>23</v>
+      </c>
+      <c r="C454" t="s">
+        <v>2470</v>
+      </c>
+      <c r="D454" t="s">
+        <v>1468</v>
+      </c>
+      <c r="G454" t="s">
+        <v>166</v>
+      </c>
+      <c r="H454" t="s">
+        <v>48</v>
+      </c>
+      <c r="I454" t="s">
+        <v>2471</v>
+      </c>
+      <c r="J454" t="s">
+        <v>2472</v>
+      </c>
+      <c r="K454" t="s">
+        <v>207</v>
+      </c>
+      <c r="L454" t="s">
+        <v>51</v>
+      </c>
+      <c r="M454" t="s">
+        <v>52</v>
+      </c>
+      <c r="N454" t="s">
+        <v>2473</v>
+      </c>
+      <c r="O454" t="s">
+        <v>723</v>
+      </c>
+      <c r="P454" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q454" t="s">
+        <v>854</v>
+      </c>
+      <c r="R454" t="s">
+        <v>57</v>
+      </c>
+      <c r="S454" t="s">
+        <v>313</v>
+      </c>
+      <c r="T454" t="s">
+        <v>58</v>
+      </c>
+      <c r="U454" t="s">
+        <v>41</v>
+      </c>
+      <c r="V454" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="455" spans="1:22">
+      <c r="A455" t="s">
+        <v>2474</v>
+      </c>
+      <c r="B455" t="s">
+        <v>23</v>
+      </c>
+      <c r="C455" t="s">
+        <v>2475</v>
+      </c>
+      <c r="D455" t="s">
+        <v>25</v>
+      </c>
+      <c r="G455" t="s">
+        <v>28</v>
+      </c>
+      <c r="H455" t="s">
+        <v>205</v>
+      </c>
+      <c r="I455" t="s">
+        <v>2476</v>
+      </c>
+      <c r="J455" t="s">
+        <v>2472</v>
+      </c>
+      <c r="K455" t="s">
+        <v>50</v>
+      </c>
+      <c r="L455" t="s">
+        <v>32</v>
+      </c>
+      <c r="M455" t="s">
+        <v>33</v>
+      </c>
+      <c r="N455" t="s">
+        <v>2477</v>
+      </c>
+      <c r="O455" t="s">
+        <v>1540</v>
+      </c>
+      <c r="P455" t="s">
+        <v>979</v>
+      </c>
+      <c r="Q455" t="s">
+        <v>221</v>
+      </c>
+      <c r="R455" t="s">
+        <v>38</v>
+      </c>
+      <c r="S455" t="s">
+        <v>965</v>
+      </c>
+      <c r="T455" t="s">
+        <v>58</v>
+      </c>
+      <c r="U455" t="s">
+        <v>73</v>
+      </c>
+      <c r="V455" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="456" spans="1:22">
+      <c r="A456" t="s">
+        <v>2478</v>
+      </c>
+      <c r="B456" t="s">
+        <v>23</v>
+      </c>
+      <c r="C456" t="s">
+        <v>2479</v>
+      </c>
+      <c r="D456" t="s">
+        <v>532</v>
+      </c>
+      <c r="G456" t="s">
+        <v>157</v>
+      </c>
+      <c r="H456" t="s">
+        <v>205</v>
+      </c>
+      <c r="I456" t="s">
+        <v>217</v>
+      </c>
+      <c r="J456" t="s">
+        <v>2480</v>
+      </c>
+      <c r="K456" t="s">
+        <v>50</v>
+      </c>
+      <c r="L456" t="s">
+        <v>32</v>
+      </c>
+      <c r="M456" t="s">
+        <v>33</v>
+      </c>
+      <c r="N456" t="s">
+        <v>2481</v>
+      </c>
+      <c r="O456" t="s">
+        <v>871</v>
+      </c>
+      <c r="P456" t="s">
+        <v>909</v>
+      </c>
+      <c r="Q456" t="s">
+        <v>56</v>
+      </c>
+      <c r="R456" t="s">
+        <v>38</v>
+      </c>
+      <c r="S456" t="s">
+        <v>257</v>
+      </c>
+      <c r="T456" t="s">
+        <v>72</v>
+      </c>
+      <c r="U456" t="s">
+        <v>85</v>
+      </c>
+      <c r="V456" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="457" spans="1:22">
+      <c r="A457" t="s">
+        <v>954</v>
+      </c>
+      <c r="B457" t="s">
+        <v>23</v>
+      </c>
+      <c r="C457" t="s">
+        <v>2482</v>
+      </c>
+      <c r="D457" t="s">
+        <v>497</v>
+      </c>
+      <c r="G457" t="s">
+        <v>157</v>
+      </c>
+      <c r="H457" t="s">
+        <v>48</v>
+      </c>
+      <c r="I457" t="s">
+        <v>49</v>
+      </c>
+      <c r="J457" t="s">
+        <v>2483</v>
+      </c>
+      <c r="K457" t="s">
+        <v>50</v>
+      </c>
+      <c r="L457" t="s">
+        <v>51</v>
+      </c>
+      <c r="M457" t="s">
+        <v>436</v>
+      </c>
+      <c r="N457" t="s">
+        <v>2484</v>
+      </c>
+      <c r="O457" t="s">
+        <v>1871</v>
+      </c>
+      <c r="P457" t="s">
+        <v>1222</v>
+      </c>
+      <c r="Q457" t="s">
+        <v>56</v>
+      </c>
+      <c r="R457" t="s">
+        <v>140</v>
+      </c>
+      <c r="S457" t="s">
+        <v>38</v>
+      </c>
+      <c r="T457" t="s">
+        <v>58</v>
+      </c>
+      <c r="U457" t="s">
+        <v>350</v>
+      </c>
+      <c r="V457" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="458" spans="1:22">
+      <c r="A458" t="s">
+        <v>2078</v>
+      </c>
+      <c r="B458" t="s">
+        <v>23</v>
+      </c>
+      <c r="C458" t="s">
+        <v>2485</v>
+      </c>
+      <c r="D458" t="s">
+        <v>512</v>
+      </c>
+      <c r="G458" t="s">
+        <v>92</v>
+      </c>
+      <c r="H458" t="s">
+        <v>205</v>
+      </c>
+      <c r="I458" t="s">
+        <v>217</v>
+      </c>
+      <c r="K458" t="s">
+        <v>50</v>
+      </c>
+      <c r="L458" t="s">
+        <v>32</v>
+      </c>
+      <c r="M458" t="s">
+        <v>436</v>
+      </c>
+      <c r="N458" t="s">
+        <v>2486</v>
+      </c>
+      <c r="O458" t="s">
+        <v>82</v>
+      </c>
+      <c r="P458" t="s">
+        <v>909</v>
+      </c>
+      <c r="Q458" t="s">
+        <v>283</v>
+      </c>
+      <c r="R458" t="s">
+        <v>211</v>
+      </c>
+      <c r="S458" t="s">
+        <v>257</v>
+      </c>
+      <c r="T458" t="s">
+        <v>72</v>
+      </c>
+      <c r="U458" t="s">
+        <v>85</v>
+      </c>
+      <c r="V458" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="459" spans="1:22">
+      <c r="A459" t="s">
+        <v>501</v>
+      </c>
+      <c r="B459" t="s">
+        <v>23</v>
+      </c>
+      <c r="C459" t="s">
+        <v>2487</v>
+      </c>
+      <c r="D459" t="s">
+        <v>2228</v>
+      </c>
+      <c r="G459" t="s">
+        <v>28</v>
+      </c>
+      <c r="H459" t="s">
+        <v>48</v>
+      </c>
+      <c r="I459" t="s">
+        <v>2471</v>
+      </c>
+      <c r="J459" t="s">
+        <v>2488</v>
+      </c>
+      <c r="K459" t="s">
+        <v>207</v>
+      </c>
+      <c r="L459" t="s">
+        <v>51</v>
+      </c>
+      <c r="M459" t="s">
+        <v>52</v>
+      </c>
+      <c r="N459" t="s">
+        <v>2489</v>
+      </c>
+      <c r="O459" t="s">
+        <v>2116</v>
+      </c>
+      <c r="P459" t="s">
+        <v>972</v>
+      </c>
+      <c r="Q459" t="s">
+        <v>854</v>
+      </c>
+      <c r="R459" t="s">
+        <v>57</v>
+      </c>
+      <c r="S459" t="s">
+        <v>313</v>
+      </c>
+      <c r="T459" t="s">
+        <v>58</v>
+      </c>
+      <c r="U459" t="s">
+        <v>41</v>
+      </c>
+      <c r="V459" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="460" spans="1:22">
+      <c r="A460" t="s">
+        <v>2490</v>
+      </c>
+      <c r="B460" t="s">
+        <v>75</v>
+      </c>
+      <c r="C460" t="s">
+        <v>2491</v>
+      </c>
+      <c r="D460" t="s">
+        <v>443</v>
+      </c>
+      <c r="G460" t="s">
+        <v>65</v>
+      </c>
+      <c r="H460" t="s">
+        <v>289</v>
+      </c>
+      <c r="I460" t="s">
+        <v>290</v>
+      </c>
+      <c r="J460" t="s">
+        <v>187</v>
+      </c>
+      <c r="K460" t="s">
+        <v>207</v>
+      </c>
+      <c r="L460" t="s">
+        <v>32</v>
+      </c>
+      <c r="M460" t="s">
+        <v>52</v>
+      </c>
+      <c r="N460" t="s">
+        <v>2404</v>
+      </c>
+      <c r="O460" t="s">
+        <v>2159</v>
+      </c>
+      <c r="P460" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q460" t="s">
+        <v>902</v>
+      </c>
+      <c r="R460" t="s">
+        <v>211</v>
+      </c>
+      <c r="S460" t="s">
+        <v>294</v>
+      </c>
+      <c r="T460" t="s">
+        <v>180</v>
+      </c>
+      <c r="U460" t="s">
+        <v>117</v>
+      </c>
+      <c r="V460" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="461" spans="1:22">
+      <c r="A461" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B461" t="s">
+        <v>23</v>
+      </c>
+      <c r="C461" t="s">
+        <v>2493</v>
+      </c>
+      <c r="D461" t="s">
+        <v>2494</v>
+      </c>
+      <c r="G461" t="s">
+        <v>166</v>
+      </c>
+      <c r="H461" t="s">
+        <v>289</v>
+      </c>
+      <c r="I461" t="s">
+        <v>1697</v>
+      </c>
+      <c r="K461" t="s">
+        <v>207</v>
+      </c>
+      <c r="L461" t="s">
+        <v>427</v>
+      </c>
+      <c r="M461" t="s">
+        <v>52</v>
+      </c>
+      <c r="N461" t="s">
+        <v>1743</v>
+      </c>
+      <c r="O461" t="s">
+        <v>871</v>
+      </c>
+      <c r="P461" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q461" t="s">
+        <v>1229</v>
+      </c>
+      <c r="R461" t="s">
+        <v>38</v>
+      </c>
+      <c r="S461" t="s">
+        <v>294</v>
+      </c>
+      <c r="T461" t="s">
+        <v>40</v>
+      </c>
+      <c r="U461" t="s">
+        <v>314</v>
+      </c>
+      <c r="V461" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="462" spans="1:22">
+      <c r="A462" t="s">
+        <v>2495</v>
+      </c>
+      <c r="B462" t="s">
+        <v>23</v>
+      </c>
+      <c r="C462" t="s">
+        <v>2496</v>
+      </c>
+      <c r="D462" t="s">
+        <v>2497</v>
+      </c>
+      <c r="G462" t="s">
+        <v>65</v>
+      </c>
+      <c r="H462" t="s">
+        <v>48</v>
+      </c>
+      <c r="I462" t="s">
+        <v>2471</v>
+      </c>
+      <c r="J462" t="s">
+        <v>2498</v>
+      </c>
+      <c r="K462" t="s">
+        <v>207</v>
+      </c>
+      <c r="L462" t="s">
+        <v>51</v>
+      </c>
+      <c r="M462" t="s">
+        <v>33</v>
+      </c>
+      <c r="N462" t="s">
+        <v>2499</v>
+      </c>
+      <c r="O462" t="s">
+        <v>2500</v>
+      </c>
+      <c r="P462" t="s">
+        <v>419</v>
+      </c>
+      <c r="Q462" t="s">
+        <v>1147</v>
+      </c>
+      <c r="R462" t="s">
+        <v>57</v>
+      </c>
+      <c r="S462" t="s">
+        <v>69</v>
+      </c>
+      <c r="T462" t="s">
+        <v>58</v>
+      </c>
+      <c r="U462" t="s">
+        <v>96</v>
+      </c>
+      <c r="V462" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="463" spans="1:22">
+      <c r="A463" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B463" t="s">
+        <v>23</v>
+      </c>
+      <c r="C463" t="s">
+        <v>2501</v>
+      </c>
+      <c r="D463" t="s">
+        <v>2502</v>
+      </c>
+      <c r="G463" t="s">
+        <v>28</v>
+      </c>
+      <c r="H463" t="s">
+        <v>29</v>
+      </c>
+      <c r="I463" t="s">
+        <v>365</v>
+      </c>
+      <c r="J463" t="s">
+        <v>2503</v>
+      </c>
+      <c r="K463" t="s">
+        <v>31</v>
+      </c>
+      <c r="L463" t="s">
+        <v>32</v>
+      </c>
+      <c r="M463" t="s">
+        <v>52</v>
+      </c>
+      <c r="N463" t="s">
+        <v>1186</v>
+      </c>
+      <c r="O463" t="s">
+        <v>1504</v>
+      </c>
+      <c r="P463" t="s">
+        <v>538</v>
+      </c>
+      <c r="Q463" t="s">
+        <v>916</v>
+      </c>
+      <c r="R463" t="s">
+        <v>211</v>
+      </c>
+      <c r="S463" t="s">
+        <v>522</v>
+      </c>
+      <c r="T463" t="s">
+        <v>370</v>
+      </c>
+      <c r="U463" t="s">
+        <v>348</v>
+      </c>
+      <c r="V463" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="464" spans="1:22">
+      <c r="A464" t="s">
+        <v>2504</v>
+      </c>
+      <c r="B464" t="s">
+        <v>23</v>
+      </c>
+      <c r="C464" t="s">
+        <v>2505</v>
+      </c>
+      <c r="D464" t="s">
+        <v>2506</v>
+      </c>
+      <c r="G464" t="s">
+        <v>92</v>
+      </c>
+      <c r="H464" t="s">
+        <v>205</v>
+      </c>
+      <c r="I464" t="s">
+        <v>2476</v>
+      </c>
+      <c r="J464" t="s">
+        <v>2507</v>
+      </c>
+      <c r="K464" t="s">
+        <v>50</v>
+      </c>
+      <c r="L464" t="s">
+        <v>32</v>
+      </c>
+      <c r="M464" t="s">
+        <v>52</v>
+      </c>
+      <c r="N464" t="s">
+        <v>774</v>
+      </c>
+      <c r="O464" t="s">
+        <v>1907</v>
+      </c>
+      <c r="P464" t="s">
+        <v>419</v>
+      </c>
+      <c r="Q464" t="s">
+        <v>128</v>
+      </c>
+      <c r="R464" t="s">
+        <v>211</v>
+      </c>
+      <c r="S464" t="s">
+        <v>965</v>
+      </c>
+      <c r="T464" t="s">
+        <v>58</v>
+      </c>
+      <c r="U464" t="s">
+        <v>84</v>
+      </c>
+      <c r="V464" t="s">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="465" spans="1:22">
+      <c r="A465" t="s">
+        <v>2509</v>
+      </c>
+      <c r="B465" t="s">
+        <v>75</v>
+      </c>
+      <c r="C465" t="s">
+        <v>2510</v>
+      </c>
+      <c r="D465" t="s">
+        <v>2511</v>
+      </c>
+      <c r="G465" t="s">
+        <v>186</v>
+      </c>
+      <c r="H465" t="s">
+        <v>289</v>
+      </c>
+      <c r="I465" t="s">
+        <v>1697</v>
+      </c>
+      <c r="J465" t="s">
+        <v>2512</v>
+      </c>
+      <c r="K465" t="s">
+        <v>207</v>
+      </c>
+      <c r="L465" t="s">
+        <v>32</v>
+      </c>
+      <c r="M465" t="s">
+        <v>52</v>
+      </c>
+      <c r="N465" t="s">
+        <v>1796</v>
+      </c>
+      <c r="O465" t="s">
+        <v>150</v>
+      </c>
+      <c r="P465" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q465" t="s">
+        <v>1187</v>
+      </c>
+      <c r="R465" t="s">
+        <v>211</v>
+      </c>
+      <c r="S465" t="s">
+        <v>39</v>
+      </c>
+      <c r="T465" t="s">
+        <v>40</v>
+      </c>
+      <c r="U465" t="s">
+        <v>41</v>
+      </c>
+      <c r="V465" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="466" spans="1:22">
+      <c r="A466" t="s">
+        <v>2513</v>
+      </c>
+      <c r="B466" t="s">
+        <v>23</v>
+      </c>
+      <c r="C466" t="s">
+        <v>2514</v>
+      </c>
+      <c r="D466" t="s">
+        <v>2515</v>
+      </c>
+      <c r="G466" t="s">
+        <v>166</v>
+      </c>
+      <c r="H466" t="s">
+        <v>48</v>
+      </c>
+      <c r="I466" t="s">
+        <v>66</v>
+      </c>
+      <c r="J466" t="s">
+        <v>885</v>
+      </c>
+      <c r="K466" t="s">
+        <v>50</v>
+      </c>
+      <c r="L466" t="s">
+        <v>51</v>
+      </c>
+      <c r="M466" t="s">
+        <v>52</v>
+      </c>
+      <c r="N466" t="s">
+        <v>826</v>
+      </c>
+      <c r="O466" t="s">
+        <v>1766</v>
+      </c>
+      <c r="P466" t="s">
+        <v>627</v>
+      </c>
+      <c r="Q466" t="s">
+        <v>554</v>
+      </c>
+      <c r="R466" t="s">
+        <v>57</v>
+      </c>
+      <c r="S466" t="s">
+        <v>58</v>
+      </c>
+      <c r="T466" t="s">
+        <v>72</v>
+      </c>
+      <c r="U466" t="s">
+        <v>73</v>
+      </c>
+      <c r="V466" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="467" spans="1:22">
+      <c r="A467" t="s">
+        <v>2516</v>
+      </c>
+      <c r="B467" t="s">
+        <v>23</v>
+      </c>
+      <c r="C467" t="s">
+        <v>2517</v>
+      </c>
+      <c r="D467" t="s">
+        <v>2518</v>
+      </c>
+      <c r="G467" t="s">
+        <v>166</v>
+      </c>
+      <c r="H467" t="s">
+        <v>425</v>
+      </c>
+      <c r="I467" t="s">
+        <v>1167</v>
+      </c>
+      <c r="J467" t="s">
+        <v>1577</v>
+      </c>
+      <c r="K467" t="s">
+        <v>50</v>
+      </c>
+      <c r="L467" t="s">
+        <v>427</v>
+      </c>
+      <c r="M467" t="s">
+        <v>52</v>
+      </c>
+      <c r="N467" t="s">
+        <v>2519</v>
+      </c>
+      <c r="O467" t="s">
+        <v>1345</v>
+      </c>
+      <c r="P467" t="s">
+        <v>523</v>
+      </c>
+      <c r="Q467" t="s">
+        <v>1089</v>
+      </c>
+      <c r="R467" t="s">
+        <v>211</v>
+      </c>
+      <c r="S467" t="s">
+        <v>1170</v>
+      </c>
+      <c r="T467" t="s">
+        <v>563</v>
+      </c>
+      <c r="U467" t="s">
+        <v>85</v>
+      </c>
+      <c r="V467" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="468" spans="1:22">
+      <c r="A468" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B468" t="s">
+        <v>23</v>
+      </c>
+      <c r="C468" t="s">
+        <v>2520</v>
+      </c>
+      <c r="D468" t="s">
+        <v>2521</v>
+      </c>
+      <c r="G468" t="s">
+        <v>166</v>
+      </c>
+      <c r="H468" t="s">
+        <v>425</v>
+      </c>
+      <c r="I468" t="s">
+        <v>535</v>
+      </c>
+      <c r="J468" t="s">
+        <v>1577</v>
+      </c>
+      <c r="K468" t="s">
+        <v>50</v>
+      </c>
+      <c r="L468" t="s">
+        <v>427</v>
+      </c>
+      <c r="M468" t="s">
+        <v>33</v>
+      </c>
+      <c r="N468" t="s">
+        <v>1560</v>
+      </c>
+      <c r="O468" t="s">
+        <v>688</v>
+      </c>
+      <c r="P468" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q468" t="s">
+        <v>171</v>
+      </c>
+      <c r="R468" t="s">
+        <v>38</v>
+      </c>
+      <c r="S468" t="s">
+        <v>430</v>
+      </c>
+      <c r="T468" t="s">
+        <v>58</v>
+      </c>
+      <c r="U468" t="s">
+        <v>73</v>
+      </c>
+      <c r="V468" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="469" spans="1:22">
+      <c r="A469" t="s">
+        <v>2522</v>
+      </c>
+      <c r="B469" t="s">
+        <v>23</v>
+      </c>
+      <c r="C469" t="s">
+        <v>2523</v>
+      </c>
+      <c r="D469" t="s">
+        <v>2524</v>
+      </c>
+      <c r="G469" t="s">
+        <v>92</v>
+      </c>
+      <c r="H469" t="s">
+        <v>134</v>
+      </c>
+      <c r="I469" t="s">
+        <v>147</v>
+      </c>
+      <c r="J469" t="s">
+        <v>1577</v>
+      </c>
+      <c r="K469" t="s">
+        <v>50</v>
+      </c>
+      <c r="L469" t="s">
+        <v>51</v>
+      </c>
+      <c r="M469" t="s">
+        <v>52</v>
+      </c>
+      <c r="N469" t="s">
+        <v>2525</v>
+      </c>
+      <c r="O469" t="s">
+        <v>188</v>
+      </c>
+      <c r="P469" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q469" t="s">
+        <v>151</v>
+      </c>
+      <c r="R469" t="s">
+        <v>140</v>
+      </c>
+      <c r="S469" t="s">
+        <v>38</v>
+      </c>
+      <c r="T469" t="s">
+        <v>40</v>
+      </c>
+      <c r="U469" t="s">
+        <v>554</v>
+      </c>
+      <c r="V469" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="470" spans="1:22">
+      <c r="A470" t="s">
+        <v>2526</v>
+      </c>
+      <c r="B470" t="s">
+        <v>23</v>
+      </c>
+      <c r="C470" t="s">
+        <v>2527</v>
+      </c>
+      <c r="D470" t="s">
+        <v>2528</v>
+      </c>
+      <c r="G470" t="s">
+        <v>65</v>
+      </c>
+      <c r="H470" t="s">
+        <v>289</v>
+      </c>
+      <c r="I470" t="s">
+        <v>1697</v>
+      </c>
+      <c r="J470" t="s">
+        <v>401</v>
+      </c>
+      <c r="K470" t="s">
+        <v>207</v>
+      </c>
+      <c r="L470" t="s">
+        <v>427</v>
+      </c>
+      <c r="M470" t="s">
+        <v>52</v>
+      </c>
+      <c r="N470" t="s">
+        <v>2529</v>
+      </c>
+      <c r="O470" t="s">
+        <v>1766</v>
+      </c>
+      <c r="P470" t="s">
+        <v>840</v>
+      </c>
+      <c r="Q470" t="s">
+        <v>127</v>
+      </c>
+      <c r="R470" t="s">
+        <v>211</v>
+      </c>
+      <c r="S470" t="s">
+        <v>294</v>
+      </c>
+      <c r="T470" t="s">
+        <v>40</v>
+      </c>
+      <c r="U470" t="s">
+        <v>314</v>
+      </c>
+      <c r="V470" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:V453" etc:filterBottomFollowUsedRange="0">
+  <autoFilter ref="A1:V453" ns1:filterBottomFollowUsedRange="0">
     <sortState ref="A1:V453">
       <sortCondition ref="A1:A453"/>
     </sortState>
